--- a/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
+++ b/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\2026\app VACUNACION ANTIRRAVICA 2025 - 2026\Animal desconocido 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B6B4D-737E-479E-B4E9-B30D8D569758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246D198-C752-4509-8423-A8F87886D6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="119">
   <si>
     <t>FUNCIONARIO</t>
   </si>
@@ -271,6 +271,120 @@
   </si>
   <si>
     <t>1.196991, -76.909065</t>
+  </si>
+  <si>
+    <t>bee2b233</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>ALFONZO LOPEZ</t>
+  </si>
+  <si>
+    <t>Esquina de la bomba que está cerca al sementerio</t>
+  </si>
+  <si>
+    <t>Tamaño mediano, semi peludo</t>
+  </si>
+  <si>
+    <t>Negro cafe</t>
+  </si>
+  <si>
+    <t>JOVEN</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/bee2b233.FOTO_ANIMAL.182107.jpg</t>
+  </si>
+  <si>
+    <t>1.152743, -77.002143</t>
+  </si>
+  <si>
+    <t>a2e5f159</t>
+  </si>
+  <si>
+    <t>CRISTO REY</t>
+  </si>
+  <si>
+    <t>Cristo rey</t>
+  </si>
+  <si>
+    <t>GRANDE</t>
+  </si>
+  <si>
+    <t>ENFERMO</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/a2e5f159.FOTO_ANIMAL.135407.jpg</t>
+  </si>
+  <si>
+    <t>TERCERA AGRESION</t>
+  </si>
+  <si>
+    <t>0.663760, -76.863030</t>
+  </si>
+  <si>
+    <t>d680ce12</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Callejón barrio los estudiantes</t>
+  </si>
+  <si>
+    <t>Pelo liso</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/d680ce12.FOTO_ANIMAL.213159.jpg</t>
+  </si>
+  <si>
+    <t>1.147752, -77.003167</t>
+  </si>
+  <si>
+    <t>f620b715</t>
+  </si>
+  <si>
+    <t>VILLA LUISA</t>
+  </si>
+  <si>
+    <t>Calle nueva</t>
+  </si>
+  <si>
+    <t>Mediano</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/f620b715.FOTO_ANIMAL.181618.jpg</t>
+  </si>
+  <si>
+    <t>Su nombre es negra</t>
+  </si>
+  <si>
+    <t>1.147609, -76.997930</t>
+  </si>
+  <si>
+    <t>db9f382d</t>
+  </si>
+  <si>
+    <t>TRIUNFO</t>
+  </si>
+  <si>
+    <t>Última cuadra del barrio el Triunfo</t>
+  </si>
+  <si>
+    <t>Rotwailer y labrador</t>
+  </si>
+  <si>
+    <t>Blanco negro</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/db9f382d.FOTO_ANIMAL.234252.jpg</t>
+  </si>
+  <si>
+    <t>1.147099, -76.997906</t>
   </si>
 </sst>
 </file>
@@ -355,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,11 +501,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -605,7 +733,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
@@ -1007,7 +1135,296 @@
         <v>80</v>
       </c>
     </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" s="5"/>
+      <c r="U7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V7" s="5"/>
+      <c r="W7" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46276</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T8" s="5"/>
+      <c r="U8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V8" s="5"/>
+      <c r="W8" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46281</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="T9" s="5"/>
+      <c r="U9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V9" s="5"/>
+      <c r="W9" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46282</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="T10" s="5"/>
+      <c r="U10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46283</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
+++ b/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\2026\app VACUNACION ANTIRRAVICA 2025 - 2026\Animal desconocido 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9246D198-C752-4509-8423-A8F87886D6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCCDAAA-69AB-4556-8619-528B78BAC0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="128">
   <si>
     <t>FUNCIONARIO</t>
   </si>
@@ -385,6 +385,33 @@
   </si>
   <si>
     <t>1.147099, -76.997906</t>
+  </si>
+  <si>
+    <t>d1b17651</t>
+  </si>
+  <si>
+    <t>PUERTO GUZMAN</t>
+  </si>
+  <si>
+    <t>CASANOVA</t>
+  </si>
+  <si>
+    <t>Orejón largo</t>
+  </si>
+  <si>
+    <t>Blanco Con rojo</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/d1b17651.FOTO_ANIMAL.175927.jpg</t>
+  </si>
+  <si>
+    <t>CHRISTIAN ANDRES YATACUE CUICUE</t>
+  </si>
+  <si>
+    <t>Mantiene en la calle</t>
+  </si>
+  <si>
+    <t>0.967583, -76.405852</t>
   </si>
 </sst>
 </file>
@@ -733,7 +760,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
@@ -1421,6 +1448,62 @@
         <v>118</v>
       </c>
     </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46290</v>
+      </c>
+      <c r="C12" s="2">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
+++ b/Animal desconocido 2026/ANIMAL DESCONOCIDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\2026\app VACUNACION ANTIRRAVICA 2025 - 2026\Animal desconocido 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCCDAAA-69AB-4556-8619-528B78BAC0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD19CEE-4A9A-4D34-98EA-B4BC8A943721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="151">
   <si>
     <t>FUNCIONARIO</t>
   </si>
@@ -412,6 +412,75 @@
   </si>
   <si>
     <t>0.967583, -76.405852</t>
+  </si>
+  <si>
+    <t>ac0ced30</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>CIUDAD JARDIN</t>
+  </si>
+  <si>
+    <t>Ciudad jardin calle nueva</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/ac0ced30.FOTO_ANIMAL.191635.jpg</t>
+  </si>
+  <si>
+    <t>Siempre muerden</t>
+  </si>
+  <si>
+    <t>1.197100, -76.910192</t>
+  </si>
+  <si>
+    <t>ff91691e</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>Mona. Tamaño mediano</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/ff91691e.FOTO_ANIMAL.191656.jpg</t>
+  </si>
+  <si>
+    <t>SEGUNDA AGRESION</t>
+  </si>
+  <si>
+    <t>Persigue motos</t>
+  </si>
+  <si>
+    <t>Son de la comunidad</t>
+  </si>
+  <si>
+    <t>1.197076, -76.910218</t>
+  </si>
+  <si>
+    <t>1faad37f</t>
+  </si>
+  <si>
+    <t>URBANIZACION SIBUNDOY</t>
+  </si>
+  <si>
+    <t>Manzana A</t>
+  </si>
+  <si>
+    <t>Tamaño mediano</t>
+  </si>
+  <si>
+    <t>ANIMAL_CALLE_Images/1faad37f.FOTO_ANIMAL.233001.jpg</t>
+  </si>
+  <si>
+    <t>Su nombre es mono</t>
+  </si>
+  <si>
+    <t>1.185220, -76.977317</t>
   </si>
 </sst>
 </file>
@@ -760,7 +829,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
@@ -1504,6 +1573,200 @@
         <v>127</v>
       </c>
     </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46302.442893518521</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T13" s="5"/>
+      <c r="U13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46302.444074074083</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46304.6015625</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
